--- a/orisuma/char.xlsx
+++ b/orisuma/char.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VScode\orisuma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828DF0A2-B378-4229-8E27-964FD16A8F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D261BB-B02D-4504-818A-A12B3443D6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="261">
   <si>
     <t>ノヴァ 技データ</t>
   </si>
@@ -177,24 +177,15 @@
     <t>単発</t>
   </si>
   <si>
-    <t>右側 55° / 左側 305°</t>
-  </si>
-  <si>
     <t>7.2F (0.12秒)</t>
   </si>
   <si>
-    <t>29.4F (0.49秒)</t>
-  </si>
-  <si>
     <t>43.2F (0.72秒)</t>
   </si>
   <si>
     <t>116×66（身体全体）</t>
   </si>
   <si>
-    <t>脚のジェット噴射で勢いをつけ、固定距離約156.64px（変更前の1.8倍）を突進する。身体全体に攻撃判定があり、地形・壁への接触またはシールド命中で移動を停止する。基礎ふっとばしはやや高く、成長値は標準的。後隙が長い。</t>
-  </si>
-  <si>
     <t>dashAttack / jetRush / 内部角度 35°</t>
   </si>
   <si>
@@ -514,9 +505,6 @@
   </si>
   <si>
     <t>下スマッシュ</t>
-  </si>
-  <si>
-    <t>右側 90° / 左側 270°</t>
   </si>
   <si>
     <t>39.6F (0.66秒)</t>
@@ -813,6 +801,18 @@
   </si>
   <si>
     <t>脚のジェット噴射で勢いをつけ、腕を身体側へ構えて肩と胴体から固定距離約156.64px（変更前の1.8倍）を突進する体当たり。身体全体に攻撃判定があり、地形・壁への接触またはシールド命中で移動を停止する。基礎ふっとばしはやや高く、成長値は標準的。後隙45F。</t>
+  </si>
+  <si>
+    <t>右側 80° / 左側 280°</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>右側 55° / 左側 305°</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>右側 315° / 左側 45°</t>
+    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
@@ -1378,10 +1378,10 @@
         <v>24</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>27</v>
@@ -1428,10 +1428,10 @@
         <v>24</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>27</v>
@@ -1466,10 +1466,10 @@
         <v>40</v>
       </c>
       <c r="F8" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G8" s="3">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>41</v>
@@ -1478,10 +1478,10 @@
         <v>42</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>27</v>
@@ -1513,7 +1513,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="F9" s="5">
         <v>360</v>
@@ -1525,13 +1525,13 @@
         <v>25</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>27</v>
@@ -1540,21 +1540,21 @@
         <v>14.5</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>49</v>
@@ -1563,25 +1563,25 @@
         <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F10" s="3">
         <v>340</v>
       </c>
       <c r="G10" s="3">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>27</v>
@@ -1590,21 +1590,21 @@
         <v>14</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>21</v>
@@ -1613,25 +1613,25 @@
         <v>5</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>67</v>
+        <v>260</v>
       </c>
       <c r="F11" s="5">
-        <v>70</v>
+        <v>540</v>
       </c>
       <c r="G11" s="5">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>41</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>27</v>
@@ -1640,21 +1640,21 @@
         <v>6.5</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
@@ -1663,7 +1663,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F12" s="3">
         <v>175</v>
@@ -1672,16 +1672,16 @@
         <v>8.4</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>27</v>
@@ -1690,21 +1690,21 @@
         <v>11</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>49</v>
@@ -1713,10 +1713,10 @@
         <v>8</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F13" s="5">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="G13" s="5">
         <v>0.8</v>
@@ -1725,13 +1725,13 @@
         <v>41</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>27</v>
@@ -1740,21 +1740,21 @@
         <v>11</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>49</v>
@@ -1763,48 +1763,48 @@
         <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F14" s="3">
         <v>330</v>
       </c>
       <c r="G14" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M14" s="3">
         <v>10</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>49</v>
@@ -1813,48 +1813,48 @@
         <v>4</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F15" s="5">
         <v>160</v>
       </c>
       <c r="G15" s="5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M15" s="5">
         <v>6</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>21</v>
@@ -1863,7 +1863,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F16" s="3">
         <v>45</v>
@@ -1875,36 +1875,36 @@
         <v>25</v>
       </c>
       <c r="I16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="M16" s="3">
         <v>2.8</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>32</v>
@@ -1913,7 +1913,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F17" s="5">
         <v>45</v>
@@ -1922,39 +1922,39 @@
         <v>0.4</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="M17" s="5">
         <v>2.8</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>39</v>
@@ -1963,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F18" s="3">
         <v>45</v>
@@ -1975,95 +1975,95 @@
         <v>43</v>
       </c>
       <c r="I18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="M18" s="3">
         <v>2.8</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D19" s="5">
         <v>14</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F19" s="5">
-        <v>440</v>
+        <v>390</v>
       </c>
       <c r="G19" s="5">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M19" s="5">
         <v>20</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D20" s="3">
         <v>4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F20" s="3">
         <v>70</v>
@@ -2072,48 +2072,48 @@
         <v>12.5</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>41</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M20" s="3">
         <v>6</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D21" s="5">
         <v>12</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F21" s="5">
         <v>410</v>
@@ -2122,39 +2122,39 @@
         <v>10.5</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M21" s="5">
         <v>17</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>21</v>
@@ -2163,7 +2163,7 @@
         <v>2.5</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F22" s="3">
         <v>38</v>
@@ -2172,39 +2172,39 @@
         <v>0.45</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M22" s="3">
         <v>3.2</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>32</v>
@@ -2213,7 +2213,7 @@
         <v>2.5</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F23" s="5">
         <v>38</v>
@@ -2222,39 +2222,39 @@
         <v>0.45</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M23" s="5">
         <v>3.2</v>
       </c>
       <c r="N23" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="P23" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="O23" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="P23" s="6" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>39</v>
@@ -2263,7 +2263,7 @@
         <v>2.5</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F24" s="3">
         <v>38</v>
@@ -2272,48 +2272,48 @@
         <v>0.45</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M24" s="3">
         <v>3.2</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O24" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="P24" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="P24" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D25" s="5">
         <v>2.5</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F25" s="5">
         <v>38</v>
@@ -2325,45 +2325,45 @@
         <v>34</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M25" s="5">
         <v>3.2</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D26" s="3">
         <v>2.5</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F26" s="3">
         <v>38</v>
@@ -2372,48 +2372,48 @@
         <v>0.45</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M26" s="3">
         <v>3.2</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D27" s="5">
         <v>2.5</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F27" s="5">
         <v>38</v>
@@ -2422,48 +2422,48 @@
         <v>0.45</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M27" s="5">
         <v>3.2</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D28" s="3">
         <v>2.5</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F28" s="3">
         <v>38</v>
@@ -2472,39 +2472,39 @@
         <v>0.45</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M28" s="3">
         <v>3.2</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>49</v>
@@ -2513,7 +2513,7 @@
         <v>18</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F29" s="5">
         <v>470</v>
@@ -2522,16 +2522,16 @@
         <v>9.5</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>27</v>
@@ -2540,21 +2540,21 @@
         <v>26</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>49</v>
@@ -2563,7 +2563,7 @@
         <v>25</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F30" s="3">
         <v>470</v>
@@ -2572,16 +2572,16 @@
         <v>4.2</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>33</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>27</v>
@@ -2590,21 +2590,21 @@
         <v>36</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>49</v>
@@ -2613,7 +2613,7 @@
         <v>16</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>163</v>
+        <v>258</v>
       </c>
       <c r="F31" s="5">
         <v>300</v>
@@ -2622,16 +2622,16 @@
         <v>5.5</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>27</v>
@@ -2640,30 +2640,30 @@
         <v>23</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D32" s="3">
         <v>7.2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F32" s="3">
         <v>340</v>
@@ -2678,10 +2678,10 @@
         <v>27</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>27</v>
@@ -2690,24 +2690,24 @@
         <v>10.5</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D33" s="5">
         <v>15</v>
@@ -2722,16 +2722,16 @@
         <v>4.5</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>27</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>27</v>
@@ -2740,130 +2740,130 @@
         <v>24</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="K34" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="L34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="P34" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="P34" s="6" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="P35" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O35" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="P35" s="6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D36" s="3">
         <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>27</v>
@@ -2872,39 +2872,39 @@
         <v>27</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M36" s="3">
         <v>0</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>49</v>
@@ -2913,7 +2913,7 @@
         <v>1.6</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>27</v>
@@ -2943,21 +2943,21 @@
         <v>27</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D38" s="3">
         <v>7</v>
@@ -2972,16 +2972,16 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>27</v>
@@ -2993,27 +2993,27 @@
         <v>27</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D39" s="5">
         <v>2</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>27</v>
@@ -3028,10 +3028,10 @@
         <v>27</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L39" s="4" t="s">
         <v>27</v>
@@ -3043,27 +3043,27 @@
         <v>27</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D40" s="3">
         <v>10.5</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F40" s="3">
         <v>445</v>
@@ -3072,16 +3072,16 @@
         <v>4.2</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>27</v>
@@ -3093,27 +3093,27 @@
         <v>27</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D41" s="5">
         <v>7.5</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F41" s="5">
         <v>190</v>
@@ -3122,16 +3122,16 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>27</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="L41" s="4" t="s">
         <v>27</v>
@@ -3143,27 +3143,27 @@
         <v>27</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D42" s="3">
         <v>2</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>27</v>
@@ -3178,10 +3178,10 @@
         <v>27</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>27</v>
@@ -3193,27 +3193,27 @@
         <v>27</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D43" s="5">
         <v>2</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>27</v>
@@ -3222,48 +3222,48 @@
         <v>27</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>27</v>
       </c>
       <c r="J43" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="P43" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M43" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="P43" s="6" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D44" s="3">
         <v>2</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>27</v>
@@ -3272,16 +3272,16 @@
         <v>27</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>27</v>
@@ -3293,27 +3293,27 @@
         <v>27</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D45" s="5">
         <v>4</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F45" s="5">
         <v>365</v>
@@ -3322,16 +3322,16 @@
         <v>4.5</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>27</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>27</v>
@@ -3343,18 +3343,18 @@
         <v>27</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>49</v>
@@ -3363,7 +3363,7 @@
         <v>32.5</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F46" s="3">
         <v>540</v>
@@ -3372,16 +3372,16 @@
         <v>11.5</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>27</v>
@@ -3390,48 +3390,48 @@
         <v>32.5</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="84" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D47" s="5">
         <v>6.5</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F47" s="5">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="G47" s="5">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>42</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>44</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="L47" s="4" t="s">
         <v>27</v>
@@ -3440,13 +3440,13 @@
         <v>9</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/orisuma/char.xlsx
+++ b/orisuma/char.xlsx
@@ -14,6 +14,7 @@
   </bookViews>
   <sheets>
     <sheet name="ノヴァ" sheetId="1" r:id="rId1"/>
+    <sheet name="五条悟" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -3460,4 +3461,907 @@
   <pageMargins left="0.25" right="0.25" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="7" width="17" customWidth="1"/>
+    <col min="8" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="11" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="27" customWidth="1"/>
+    <col min="15" max="15" width="72" customWidth="1"/>
+    <col min="16" max="16" width="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="28.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>五条悟 技データ</t>
+        </is>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+    </row>
+    <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>仮実装。軽量級。1段目のジャンプ力はノヴァの1.2倍。技は未登録。角度は仕様表記（0°=真上、時計回り）。</t>
+        </is>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+    </row>
+    <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+    </row>
+    <row r="4" spans="1:16" ht="7.95" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:16" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="6"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="6"/>
+    </row>
+    <row r="19" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="6"/>
+    </row>
+    <row r="20" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="6"/>
+    </row>
+    <row r="21" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="6"/>
+    </row>
+    <row r="22" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="6"/>
+    </row>
+    <row r="24" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="6"/>
+    </row>
+    <row r="25" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="6"/>
+    </row>
+    <row r="26" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="6"/>
+    </row>
+    <row r="27" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="6"/>
+    </row>
+    <row r="29" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="6"/>
+    </row>
+    <row r="30" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="6"/>
+    </row>
+    <row r="31" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="6"/>
+    </row>
+    <row r="32" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="6"/>
+    </row>
+    <row r="33" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="6"/>
+    </row>
+    <row r="34" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="6"/>
+    </row>
+    <row r="35" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="6"/>
+    </row>
+    <row r="36" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="6"/>
+    </row>
+    <row r="37" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="6"/>
+    </row>
+    <row r="38" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="6"/>
+    </row>
+    <row r="39" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="6"/>
+    </row>
+    <row r="40" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="6"/>
+    </row>
+    <row r="41" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="6"/>
+    </row>
+    <row r="42" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="6"/>
+    </row>
+    <row r="43" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="6"/>
+    </row>
+    <row r="44" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="6"/>
+    </row>
+    <row r="45" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="6"/>
+    </row>
+    <row r="46" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="6"/>
+    </row>
+    <row r="47" spans="1:16" ht="84" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="6"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:P47" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A3:P3"/>
+  </mergeCells>
+  <phoneticPr fontId="5"/>
+  <pageMargins left="0.25" right="0.25" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>